--- a/public/downloads/MandalTowards2025.xlsx
+++ b/public/downloads/MandalTowards2025.xlsx
@@ -8,14 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="39">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -47,10 +49,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
-  </si>
-  <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_total (ms)</t>
+  </si>
+  <si>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -617,10 +619,10 @@
         <v>417</v>
       </c>
       <c r="N3" s="5">
-        <v>6221.417308330536</v>
+        <v>6221417.308330536</v>
       </c>
       <c r="O3" s="4">
-        <v>0.05719318350353042</v>
+        <v>57.19318350353042</v>
       </c>
       <c r="P3" s="5">
         <v>108779</v>
@@ -667,10 +669,10 @@
         <v>417</v>
       </c>
       <c r="N4" s="5">
-        <v>13846.42745494843</v>
+        <v>13846427.45494843</v>
       </c>
       <c r="O4" s="4">
-        <v>0.1338439803478756</v>
+        <v>133.8439803478756</v>
       </c>
       <c r="P4" s="5">
         <v>103452</v>
@@ -717,10 +719,10 @@
         <v>417</v>
       </c>
       <c r="N5" s="5">
-        <v>7950.150148630142</v>
+        <v>7950150.148630142</v>
       </c>
       <c r="O5" s="4">
-        <v>0.08609929008555771</v>
+        <v>86.09929008555771</v>
       </c>
       <c r="P5" s="5">
         <v>92337</v>
@@ -767,10 +769,10 @@
         <v>417</v>
       </c>
       <c r="N6" s="5">
-        <v>18098.08095026016</v>
+        <v>18098080.95026016</v>
       </c>
       <c r="O6" s="4">
-        <v>0.2041129275859132</v>
+        <v>204.1129275859132</v>
       </c>
       <c r="P6" s="5">
         <v>88667</v>
@@ -817,10 +819,10 @@
         <v>417</v>
       </c>
       <c r="N7" s="5">
-        <v>1952.770825386047</v>
+        <v>1952770.825386047</v>
       </c>
       <c r="O7" s="4">
-        <v>0.01475370453909886</v>
+        <v>14.75370453909886</v>
       </c>
       <c r="P7" s="5">
         <v>132358</v>
@@ -867,10 +869,10 @@
         <v>417</v>
       </c>
       <c r="N8" s="5">
-        <v>2541.804596662521</v>
+        <v>2541804.596662521</v>
       </c>
       <c r="O8" s="4">
-        <v>0.03083778703867178</v>
+        <v>30.83778703867178</v>
       </c>
       <c r="P8" s="5">
         <v>82425</v>
@@ -917,10 +919,10 @@
         <v>417</v>
       </c>
       <c r="N9" s="5">
-        <v>6785.507981300354</v>
+        <v>6785507.981300354</v>
       </c>
       <c r="O9" s="4">
-        <v>0.1058746759447707</v>
+        <v>105.8746759447707</v>
       </c>
       <c r="P9" s="5">
         <v>64090</v>
@@ -967,10 +969,10 @@
         <v>417</v>
       </c>
       <c r="N10" s="5">
-        <v>1195.934808731079</v>
+        <v>1195934.808731079</v>
       </c>
       <c r="O10" s="4">
-        <v>0.03721364186859629</v>
+        <v>37.21364186859629</v>
       </c>
       <c r="P10" s="5">
         <v>32137</v>
@@ -1017,10 +1019,10 @@
         <v>417</v>
       </c>
       <c r="N11" s="5">
-        <v>805.2302625179291</v>
+        <v>805230.2625179291</v>
       </c>
       <c r="O11" s="4">
-        <v>0.01804316264492984</v>
+        <v>18.04316264492984</v>
       </c>
       <c r="P11" s="5">
         <v>44628</v>
@@ -1067,10 +1069,10 @@
         <v>417</v>
       </c>
       <c r="N12" s="5">
-        <v>5552.124415874481</v>
+        <v>5552124.415874481</v>
       </c>
       <c r="O12" s="4">
-        <v>0.0727613086241512</v>
+        <v>72.7613086241512</v>
       </c>
       <c r="P12" s="5">
         <v>76306</v>
@@ -1098,6 +1100,613 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>78.8968824940048</v>
+      </c>
+      <c r="C3" s="3">
+        <v>14.38848920863309</v>
+      </c>
+      <c r="D3" s="3">
+        <v>6.71462829736211</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3.117505995203837</v>
+      </c>
+      <c r="F3" s="3">
+        <v>3.597122302158273</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4744147759019606</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1874748667706438</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.244361864996383</v>
+      </c>
+      <c r="K3" s="4">
+        <v>83.64108713029573</v>
+      </c>
+      <c r="L3" s="4">
+        <v>79.81662991754357</v>
+      </c>
+      <c r="M3" s="5">
+        <v>417</v>
+      </c>
+      <c r="N3" s="5">
+        <v>6221417.308330536</v>
+      </c>
+      <c r="O3" s="4">
+        <v>57.19318350353042</v>
+      </c>
+      <c r="P3" s="5">
+        <v>108779</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>82.49400479616307</v>
+      </c>
+      <c r="C4" s="3">
+        <v>10.31175059952038</v>
+      </c>
+      <c r="D4" s="3">
+        <v>7.194244604316546</v>
+      </c>
+      <c r="E4" s="3">
+        <v>5.035971223021583</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.678657074340528</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.4796163069544364</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.4429977244898529</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.1770155321093531</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.1787773016016319</v>
+      </c>
+      <c r="K4" s="4">
+        <v>87.99197376792443</v>
+      </c>
+      <c r="L4" s="4">
+        <v>84.16732385903299</v>
+      </c>
+      <c r="M4" s="5">
+        <v>417</v>
+      </c>
+      <c r="N4" s="5">
+        <v>13846427.45494843</v>
+      </c>
+      <c r="O4" s="4">
+        <v>133.8439803478756</v>
+      </c>
+      <c r="P4" s="5">
+        <v>103452</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>78.17745803357315</v>
+      </c>
+      <c r="C5" s="3">
+        <v>15.10791366906475</v>
+      </c>
+      <c r="D5" s="3">
+        <v>6.71462829736211</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4.556354916067146</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.918465227817746</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.5835851412575767</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2109288530395572</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2303192387552083</v>
+      </c>
+      <c r="K5" s="4">
+        <v>86.80639162139676</v>
+      </c>
+      <c r="L5" s="4">
+        <v>82.21626725465399</v>
+      </c>
+      <c r="M5" s="5">
+        <v>417</v>
+      </c>
+      <c r="N5" s="5">
+        <v>7950150.148630142</v>
+      </c>
+      <c r="O5" s="4">
+        <v>86.09929008555771</v>
+      </c>
+      <c r="P5" s="5">
+        <v>92337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>82.01438848920863</v>
+      </c>
+      <c r="C6" s="3">
+        <v>11.75059952038369</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6.235011990407674</v>
+      </c>
+      <c r="E6" s="3">
+        <v>4.07673860911271</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.158273381294964</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4163228363386167</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1622241270365867</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1883596125807724</v>
+      </c>
+      <c r="K6" s="4">
+        <v>89.41614055694224</v>
+      </c>
+      <c r="L6" s="4">
+        <v>84.96625518377098</v>
+      </c>
+      <c r="M6" s="5">
+        <v>417</v>
+      </c>
+      <c r="N6" s="5">
+        <v>18098080.95026016</v>
+      </c>
+      <c r="O6" s="4">
+        <v>204.1129275859132</v>
+      </c>
+      <c r="P6" s="5">
+        <v>88667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>78.8968824940048</v>
+      </c>
+      <c r="C7" s="3">
+        <v>12.23021582733813</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8.872901678657074</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2.877697841726619</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5.515587529976019</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.4796163069544364</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.4791163838933912</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.194685310555014</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.2486581378864751</v>
+      </c>
+      <c r="K7" s="4">
+        <v>88.41473759767695</v>
+      </c>
+      <c r="L7" s="4">
+        <v>83.11753281938286</v>
+      </c>
+      <c r="M7" s="5">
+        <v>417</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1952770.825386047</v>
+      </c>
+      <c r="O7" s="4">
+        <v>14.75370453909886</v>
+      </c>
+      <c r="P7" s="5">
+        <v>132358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>83.21342925659472</v>
+      </c>
+      <c r="C8" s="3">
+        <v>11.03117505995204</v>
+      </c>
+      <c r="D8" s="3">
+        <v>5.755395683453238</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3.597122302158273</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2.158273381294964</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.496322345848087</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2565391267899144</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2723595868397652</v>
+      </c>
+      <c r="K8" s="4">
+        <v>88.59288079740277</v>
+      </c>
+      <c r="L8" s="4">
+        <v>84.33940096244986</v>
+      </c>
+      <c r="M8" s="5">
+        <v>417</v>
+      </c>
+      <c r="N8" s="5">
+        <v>2541804.596662521</v>
+      </c>
+      <c r="O8" s="4">
+        <v>30.83778703867178</v>
+      </c>
+      <c r="P8" s="5">
+        <v>82425</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>84.89208633093526</v>
+      </c>
+      <c r="C9" s="3">
+        <v>11.99040767386091</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3.117505995203837</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2.637889688249401</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.4796163069544364</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4285691545759813</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.1995842422101777</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.2364491185282427</v>
+      </c>
+      <c r="K9" s="4">
+        <v>85.72611298716127</v>
+      </c>
+      <c r="L9" s="4">
+        <v>82.29851018513956</v>
+      </c>
+      <c r="M9" s="5">
+        <v>417</v>
+      </c>
+      <c r="N9" s="5">
+        <v>6785507.981300354</v>
+      </c>
+      <c r="O9" s="4">
+        <v>105.8746759447707</v>
+      </c>
+      <c r="P9" s="5">
+        <v>64090</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>89.92805755395683</v>
+      </c>
+      <c r="C10" s="3">
+        <v>8.872901678657074</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1.199040767386091</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.2398081534772182</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.9592326139088728</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.4612202010149729</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3543773331956059</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.3881038682354914</v>
+      </c>
+      <c r="K10" s="4">
+        <v>88.49410267704199</v>
+      </c>
+      <c r="L10" s="4">
+        <v>86.00043455168623</v>
+      </c>
+      <c r="M10" s="5">
+        <v>417</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1195934.808731079</v>
+      </c>
+      <c r="O10" s="4">
+        <v>37.21364186859629</v>
+      </c>
+      <c r="P10" s="5">
+        <v>32137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>84.89208633093526</v>
+      </c>
+      <c r="C11" s="3">
+        <v>13.42925659472422</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1.678657074340528</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1.678657074340528</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.432457243310518</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2495337311811333</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2864063482535195</v>
+      </c>
+      <c r="K11" s="4">
+        <v>84.43033328439287</v>
+      </c>
+      <c r="L11" s="4">
+        <v>82.07077291187071</v>
+      </c>
+      <c r="M11" s="5">
+        <v>417</v>
+      </c>
+      <c r="N11" s="5">
+        <v>805230.2625179291</v>
+      </c>
+      <c r="O11" s="4">
+        <v>18.04316264492984</v>
+      </c>
+      <c r="P11" s="5">
+        <v>44628</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>81.77458033573141</v>
+      </c>
+      <c r="C12" s="3">
+        <v>13.42925659472422</v>
+      </c>
+      <c r="D12" s="3">
+        <v>4.796163069544365</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3.357314148681055</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.43884892086331</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.4065774171712768</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1748463280735282</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.201145295970987</v>
+      </c>
+      <c r="K12" s="4">
+        <v>89.28652995970567</v>
+      </c>
+      <c r="L12" s="4">
+        <v>84.2652321096143</v>
+      </c>
+      <c r="M12" s="5">
+        <v>417</v>
+      </c>
+      <c r="N12" s="5">
+        <v>5552124.415874481</v>
+      </c>
+      <c r="O12" s="4">
+        <v>72.7613086241512</v>
+      </c>
+      <c r="P12" s="5">
+        <v>76306</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1210,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -1254,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
@@ -1298,10 +1907,10 @@
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
@@ -1342,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="L6" s="5">
         <v>0</v>
@@ -1386,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L7" s="5">
         <v>0</v>
@@ -1430,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L8" s="5">
         <v>0</v>
@@ -1474,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L9" s="5">
         <v>0</v>
@@ -1562,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
         <v>0</v>
@@ -1606,10 +2215,545 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
+        <v>6</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>329</v>
+      </c>
+      <c r="C3" s="5">
+        <v>60</v>
+      </c>
+      <c r="D3" s="5">
+        <v>28</v>
+      </c>
+      <c r="E3" s="5">
+        <v>13</v>
+      </c>
+      <c r="F3" s="5">
+        <v>15</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>13</v>
+      </c>
+      <c r="I3" s="5">
+        <v>13</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>15</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="B4" s="5">
+        <v>344</v>
+      </c>
+      <c r="C4" s="5">
+        <v>43</v>
+      </c>
+      <c r="D4" s="5">
+        <v>30</v>
+      </c>
+      <c r="E4" s="5">
+        <v>21</v>
+      </c>
+      <c r="F4" s="5">
+        <v>7</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>21</v>
+      </c>
+      <c r="I4" s="5">
+        <v>21</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>7</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>326</v>
+      </c>
+      <c r="C5" s="5">
+        <v>63</v>
+      </c>
+      <c r="D5" s="5">
+        <v>28</v>
+      </c>
+      <c r="E5" s="5">
+        <v>19</v>
+      </c>
+      <c r="F5" s="5">
+        <v>8</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>19</v>
+      </c>
+      <c r="I5" s="5">
+        <v>19</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>7</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>342</v>
+      </c>
+      <c r="C6" s="5">
+        <v>49</v>
+      </c>
+      <c r="D6" s="5">
+        <v>26</v>
+      </c>
+      <c r="E6" s="5">
+        <v>17</v>
+      </c>
+      <c r="F6" s="5">
+        <v>9</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>17</v>
+      </c>
+      <c r="I6" s="5">
+        <v>17</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>9</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>329</v>
+      </c>
+      <c r="C7" s="5">
+        <v>51</v>
+      </c>
+      <c r="D7" s="5">
+        <v>37</v>
+      </c>
+      <c r="E7" s="5">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5">
+        <v>23</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5">
+        <v>12</v>
+      </c>
+      <c r="I7" s="5">
+        <v>12</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>23</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>347</v>
+      </c>
+      <c r="C8" s="5">
+        <v>46</v>
+      </c>
+      <c r="D8" s="5">
+        <v>24</v>
+      </c>
+      <c r="E8" s="5">
+        <v>15</v>
+      </c>
+      <c r="F8" s="5">
+        <v>9</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>15</v>
+      </c>
+      <c r="I8" s="5">
+        <v>15</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>9</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>354</v>
+      </c>
+      <c r="C9" s="5">
+        <v>50</v>
+      </c>
+      <c r="D9" s="5">
+        <v>13</v>
+      </c>
+      <c r="E9" s="5">
+        <v>11</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>11</v>
+      </c>
+      <c r="I9" s="5">
+        <v>11</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>2</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>375</v>
+      </c>
+      <c r="C10" s="5">
+        <v>37</v>
+      </c>
+      <c r="D10" s="5">
+        <v>5</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5">
+        <v>4</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>354</v>
+      </c>
+      <c r="C11" s="5">
+        <v>56</v>
+      </c>
+      <c r="D11" s="5">
+        <v>7</v>
+      </c>
+      <c r="E11" s="5">
+        <v>7</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>7</v>
+      </c>
+      <c r="I11" s="5">
+        <v>7</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>341</v>
+      </c>
+      <c r="C12" s="5">
+        <v>56</v>
+      </c>
+      <c r="D12" s="5">
+        <v>20</v>
+      </c>
+      <c r="E12" s="5">
+        <v>14</v>
+      </c>
+      <c r="F12" s="5">
+        <v>6</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>14</v>
+      </c>
+      <c r="I12" s="5">
+        <v>14</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>6</v>
+      </c>
       <c r="L12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>

--- a/public/downloads/MandalTowards2025.xlsx
+++ b/public/downloads/MandalTowards2025.xlsx
@@ -1208,13 +1208,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4744147759019606</v>
+        <v>0.4775265588688606</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1874748667706438</v>
+        <v>0.1840150534247423</v>
       </c>
       <c r="J3" s="4">
-        <v>0.244361864996383</v>
+        <v>0.2416386770104657</v>
       </c>
       <c r="K3" s="4">
         <v>83.64108713029573</v>
@@ -1240,13 +1240,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>82.49400479616307</v>
+        <v>82.01438848920863</v>
       </c>
       <c r="C4" s="3">
         <v>10.31175059952038</v>
       </c>
       <c r="D4" s="3">
-        <v>7.194244604316546</v>
+        <v>7.673860911270983</v>
       </c>
       <c r="E4" s="3">
         <v>5.035971223021583</v>
@@ -1255,16 +1255,16 @@
         <v>1.678657074340528</v>
       </c>
       <c r="G4" s="3">
-        <v>0.4796163069544364</v>
+        <v>0.9592326139088728</v>
       </c>
       <c r="H4" s="4">
-        <v>0.4429977244898529</v>
+        <v>0.4455558579164098</v>
       </c>
       <c r="I4" s="4">
-        <v>0.1770155321093531</v>
+        <v>0.1459713252892462</v>
       </c>
       <c r="J4" s="4">
-        <v>0.1787773016016319</v>
+        <v>0.1669020418580272</v>
       </c>
       <c r="K4" s="4">
         <v>87.99197376792443</v>
@@ -1308,13 +1308,13 @@
         <v>0.2398081534772182</v>
       </c>
       <c r="H5" s="4">
-        <v>0.5835851412575767</v>
+        <v>0.5910009363065332</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2109288530395572</v>
+        <v>0.2025373476410338</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2303192387552083</v>
+        <v>0.2280553737329047</v>
       </c>
       <c r="K5" s="4">
         <v>86.80639162139676</v>
@@ -1340,13 +1340,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>82.01438848920863</v>
+        <v>81.5347721822542</v>
       </c>
       <c r="C6" s="3">
         <v>11.75059952038369</v>
       </c>
       <c r="D6" s="3">
-        <v>6.235011990407674</v>
+        <v>6.71462829736211</v>
       </c>
       <c r="E6" s="3">
         <v>4.07673860911271</v>
@@ -1355,16 +1355,16 @@
         <v>2.158273381294964</v>
       </c>
       <c r="G6" s="3">
-        <v>0</v>
+        <v>0.4796163069544364</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4163228363386167</v>
+        <v>0.4172795168433855</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1622241270365867</v>
+        <v>0.1390380653662679</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1883596125807724</v>
+        <v>0.1672874711017581</v>
       </c>
       <c r="K6" s="4">
         <v>89.41614055694224</v>
@@ -1408,13 +1408,13 @@
         <v>0.4796163069544364</v>
       </c>
       <c r="H7" s="4">
-        <v>0.4791163838933912</v>
+        <v>0.4743183470732041</v>
       </c>
       <c r="I7" s="4">
-        <v>0.194685310555014</v>
+        <v>0.176170441236133</v>
       </c>
       <c r="J7" s="4">
-        <v>0.2486581378864751</v>
+        <v>0.2488362365797424</v>
       </c>
       <c r="K7" s="4">
         <v>88.41473759767695</v>
@@ -1458,13 +1458,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.496322345848087</v>
+        <v>0.4924873936994161</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2565391267899144</v>
+        <v>0.2322557762421205</v>
       </c>
       <c r="J8" s="4">
-        <v>0.2723595868397652</v>
+        <v>0.2435211029628517</v>
       </c>
       <c r="K8" s="4">
         <v>88.59288079740277</v>
@@ -1490,13 +1490,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>84.89208633093526</v>
+        <v>84.41247002398082</v>
       </c>
       <c r="C9" s="3">
         <v>11.99040767386091</v>
       </c>
       <c r="D9" s="3">
-        <v>3.117505995203837</v>
+        <v>3.597122302158273</v>
       </c>
       <c r="E9" s="3">
         <v>2.637889688249401</v>
@@ -1505,16 +1505,16 @@
         <v>0.4796163069544364</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>0.4796163069544364</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4285691545759813</v>
+        <v>0.4262459759711521</v>
       </c>
       <c r="I9" s="4">
-        <v>0.1995842422101777</v>
+        <v>0.1782157774966955</v>
       </c>
       <c r="J9" s="4">
-        <v>0.2364491185282427</v>
+        <v>0.2089196318028229</v>
       </c>
       <c r="K9" s="4">
         <v>85.72611298716127</v>
@@ -1540,13 +1540,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="3">
-        <v>89.92805755395683</v>
+        <v>87.29016786570743</v>
       </c>
       <c r="C10" s="3">
         <v>8.872901678657074</v>
       </c>
       <c r="D10" s="3">
-        <v>1.199040767386091</v>
+        <v>3.836930455635491</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -1555,16 +1555,16 @@
         <v>0.2398081534772182</v>
       </c>
       <c r="G10" s="3">
-        <v>0.9592326139088728</v>
+        <v>3.597122302158273</v>
       </c>
       <c r="H10" s="4">
-        <v>0.4612202010149729</v>
+        <v>0.453930553698761</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3543773331956059</v>
+        <v>0.2436839305189714</v>
       </c>
       <c r="J10" s="4">
-        <v>0.3881038682354914</v>
+        <v>0.3126886552883324</v>
       </c>
       <c r="K10" s="4">
         <v>88.49410267704199</v>
@@ -1590,13 +1590,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>84.89208633093526</v>
+        <v>84.65227817745803</v>
       </c>
       <c r="C11" s="3">
         <v>13.42925659472422</v>
       </c>
       <c r="D11" s="3">
-        <v>1.678657074340528</v>
+        <v>1.918465227817746</v>
       </c>
       <c r="E11" s="3">
         <v>1.678657074340528</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="3">
-        <v>0</v>
+        <v>0.2398081534772182</v>
       </c>
       <c r="H11" s="4">
-        <v>0.432457243310518</v>
+        <v>0.4342044297613155</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2495337311811333</v>
+        <v>0.2254113615991279</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2864063482535195</v>
+        <v>0.2345600822361193</v>
       </c>
       <c r="K11" s="4">
         <v>84.43033328439287</v>
@@ -1640,13 +1640,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>81.77458033573141</v>
+        <v>81.29496402877699</v>
       </c>
       <c r="C12" s="3">
         <v>13.42925659472422</v>
       </c>
       <c r="D12" s="3">
-        <v>4.796163069544365</v>
+        <v>5.275779376498801</v>
       </c>
       <c r="E12" s="3">
         <v>3.357314148681055</v>
@@ -1655,16 +1655,16 @@
         <v>1.43884892086331</v>
       </c>
       <c r="G12" s="3">
-        <v>0</v>
+        <v>0.4796163069544364</v>
       </c>
       <c r="H12" s="4">
-        <v>0.4065774171712768</v>
+        <v>0.4077414919969667</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1748463280735282</v>
+        <v>0.1547182178750684</v>
       </c>
       <c r="J12" s="4">
-        <v>0.201145295970987</v>
+        <v>0.1796730984415253</v>
       </c>
       <c r="K12" s="4">
         <v>89.28652995970567</v>
@@ -2371,13 +2371,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="5">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C4" s="5">
         <v>43</v>
       </c>
       <c r="D4" s="5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" s="5">
         <v>21</v>
@@ -2386,7 +2386,7 @@
         <v>7</v>
       </c>
       <c r="G4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" s="5">
         <v>21</v>
@@ -2459,13 +2459,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C6" s="5">
         <v>49</v>
       </c>
       <c r="D6" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="5">
         <v>17</v>
@@ -2474,7 +2474,7 @@
         <v>9</v>
       </c>
       <c r="G6" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="5">
         <v>17</v>
@@ -2591,13 +2591,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C9" s="5">
         <v>50</v>
       </c>
       <c r="D9" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" s="5">
         <v>11</v>
@@ -2606,7 +2606,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" s="5">
         <v>11</v>
@@ -2635,13 +2635,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="5">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="C10" s="5">
         <v>37</v>
       </c>
       <c r="D10" s="5">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E10" s="5">
         <v>0</v>
@@ -2650,7 +2650,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="5">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H10" s="5">
         <v>0</v>
@@ -2679,13 +2679,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C11" s="5">
         <v>56</v>
       </c>
       <c r="D11" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="5">
         <v>7</v>
@@ -2723,13 +2723,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C12" s="5">
         <v>56</v>
       </c>
       <c r="D12" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E12" s="5">
         <v>14</v>
@@ -2738,7 +2738,7 @@
         <v>6</v>
       </c>
       <c r="G12" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" s="5">
         <v>14</v>
